--- a/output/anova_significance_comparison.xlsx
+++ b/output/anova_significance_comparison.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7105</v>
+        <v>0.9146</v>
       </c>
       <c r="C2" t="n">
-        <v>0.774</v>
+        <v>0.9532</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1415</v>
+        <v>0.2488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2321</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0273</v>
+        <v>0.0141</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0828</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0944</v>
+        <v>0.0866</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0034</v>
+        <v>0.0018</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0985</v>
+        <v>0.0921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0622</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0534</v>
+        <v>0.0601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5851</v>
+        <v>0.6985</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5817</v>
+        <v>0.5038</v>
       </c>
     </row>
     <row r="6">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5473</v>
+        <v>0.6998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6877</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6701</v>
+        <v>0.7251</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4557</v>
+        <v>0.4276</v>
       </c>
     </row>
     <row r="7">
@@ -555,13 +555,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0033</v>
+        <v>0.0019</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1064</v>
+        <v>0.0808</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.1715</v>
+        <v>0.2521</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1927</v>
+        <v>0.1796</v>
       </c>
     </row>
     <row r="9">
@@ -588,10 +588,10 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.013</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0648</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -603,10 +603,10 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.0029</v>
+        <v>0.0011</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1256</v>
+        <v>0.1251</v>
       </c>
     </row>
     <row r="11">
@@ -618,10 +618,10 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.3145</v>
+        <v>0.2842</v>
       </c>
       <c r="E11" t="n">
-        <v>0.975</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12">
@@ -633,10 +633,10 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.9902</v>
+        <v>0.6519</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7071</v>
+        <v>0.8682</v>
       </c>
     </row>
     <row r="13">
@@ -648,10 +648,10 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5593</v>
+        <v>0.1878</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5163</v>
+        <v>0.899</v>
       </c>
     </row>
   </sheetData>
